--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C61CA0-3DE8-48C0-9D09-2B1AEABB5D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C55664F-ACE2-4E65-85E6-5A96A37F5EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -613,7 +613,9 @@
       <c r="G1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="8"/>
+      <c r="H1" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
@@ -720,6 +722,9 @@
       <c r="G2" s="8">
         <v>46064</v>
       </c>
+      <c r="H2" s="8">
+        <v>46077</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -784,6 +789,9 @@
         <v>36</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -884,6 +892,9 @@
       <c r="G4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -982,6 +993,9 @@
       <c r="G5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1080,6 +1094,9 @@
       <c r="G6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1178,6 +1195,9 @@
       <c r="G7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1276,6 +1296,9 @@
       <c r="G8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1374,6 +1397,9 @@
       <c r="G9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1472,6 +1498,9 @@
       <c r="G10" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="H10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1570,6 +1599,9 @@
       <c r="G11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1668,6 +1700,9 @@
       <c r="G12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1766,6 +1801,9 @@
       <c r="G13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -1864,6 +1902,9 @@
       <c r="G14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -1962,6 +2003,9 @@
       <c r="G15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2060,6 +2104,9 @@
       <c r="G16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2158,6 +2205,9 @@
       <c r="G17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2256,6 +2306,9 @@
       <c r="G18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2354,6 +2407,9 @@
       <c r="G19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2452,6 +2508,9 @@
       <c r="G20" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H20" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2550,6 +2609,9 @@
       <c r="G21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2648,6 +2710,9 @@
       <c r="G22" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="H22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -2746,6 +2811,9 @@
       <c r="G23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -2844,6 +2912,9 @@
       <c r="G24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -2942,6 +3013,9 @@
       <c r="G25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3040,6 +3114,9 @@
       <c r="G26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3138,6 +3215,9 @@
       <c r="G27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3236,6 +3316,9 @@
       <c r="G28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3334,6 +3417,9 @@
       <c r="G29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3432,6 +3518,9 @@
       <c r="G30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3530,6 +3619,9 @@
       <c r="G31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -3628,6 +3720,9 @@
       <c r="G32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -3726,6 +3821,9 @@
       <c r="G33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -3824,6 +3922,9 @@
       <c r="G34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -3919,13 +4020,16 @@
       <c r="G35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="H35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 H4:AZ10 BE4:BJ10 G4:G19 BK4:DG33 F4:F35 H11:BA19 BC11:BJ22 G20:BA20 H21:BA22 G21:G35 H23:BJ33">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 I4:AZ10 BE4:BJ10 BK4:DG33 BC11:BJ22 I23:BJ33 I11:BA22 F4:H35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C55664F-ACE2-4E65-85E6-5A96A37F5EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055C33A7-DA74-4ADE-ABDD-560DE01AAF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>Nicolas Gonçalves Feitosa de Jesus</t>
+  </si>
+  <si>
+    <t>4Faltas</t>
   </si>
 </sst>
 </file>
@@ -893,7 +896,7 @@
         <v>36</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
@@ -4029,7 +4032,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 I4:AZ10 BE4:BJ10 BK4:DG33 BC11:BJ22 I23:BJ33 I11:BA22 F4:H35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 I4:AZ10 BE4:BJ10 BK4:DG33 F4:H35 I11:BA22 BC11:BJ22 I23:BJ33">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055C33A7-DA74-4ADE-ABDD-560DE01AAF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77973B9C-B214-451B-9834-58BAAC908816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -619,7 +619,9 @@
       <c r="H1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="8"/>
+      <c r="I1" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
@@ -728,6 +730,9 @@
       <c r="H2" s="8">
         <v>46077</v>
       </c>
+      <c r="I2" s="8">
+        <v>46078</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -795,6 +800,9 @@
         <v>36</v>
       </c>
       <c r="H3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -898,6 +906,9 @@
       <c r="H4" s="9" t="s">
         <v>45</v>
       </c>
+      <c r="I4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -999,6 +1010,9 @@
       <c r="H5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1100,6 +1114,9 @@
       <c r="H6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1201,6 +1218,9 @@
       <c r="H7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1302,6 +1322,9 @@
       <c r="H8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1403,6 +1426,9 @@
       <c r="H9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1504,6 +1530,9 @@
       <c r="H10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1605,6 +1634,9 @@
       <c r="H11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1706,6 +1738,9 @@
       <c r="H12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1807,6 +1842,9 @@
       <c r="H13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -1908,6 +1946,9 @@
       <c r="H14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2009,6 +2050,9 @@
       <c r="H15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2110,6 +2154,9 @@
       <c r="H16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2211,6 +2258,9 @@
       <c r="H17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2312,6 +2362,9 @@
       <c r="H18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2413,6 +2466,9 @@
       <c r="H19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2514,6 +2570,9 @@
       <c r="H20" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I20" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2615,6 +2674,9 @@
       <c r="H21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2716,6 +2778,9 @@
       <c r="H22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -2817,6 +2882,9 @@
       <c r="H23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -2918,6 +2986,9 @@
       <c r="H24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3019,6 +3090,9 @@
       <c r="H25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3120,6 +3194,9 @@
       <c r="H26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3221,6 +3298,9 @@
       <c r="H27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3322,6 +3402,9 @@
       <c r="H28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3423,6 +3506,9 @@
       <c r="H29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3524,6 +3610,9 @@
       <c r="H30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3625,6 +3714,9 @@
       <c r="H31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -3726,6 +3818,9 @@
       <c r="H32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -3827,6 +3922,9 @@
       <c r="H33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -3928,6 +4026,9 @@
       <c r="H34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4026,13 +4127,16 @@
       <c r="H35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="I35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 I4:AZ10 BE4:BJ10 BK4:DG33 F4:H35 I11:BA22 BC11:BJ22 I23:BJ33">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 J4:AZ10 BE4:BJ10 BK4:DG33 J11:BA22 BC11:BJ22 J23:BJ33 F4:I35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77973B9C-B214-451B-9834-58BAAC908816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE70E011-E403-4E97-908E-59A58E185259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atividades!$A$1:$C$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -622,7 +623,9 @@
       <c r="I1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="8"/>
+      <c r="J1" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
@@ -733,6 +736,9 @@
       <c r="I2" s="8">
         <v>46078</v>
       </c>
+      <c r="J2" s="8">
+        <v>46084</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -803,6 +809,9 @@
         <v>36</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -909,6 +918,9 @@
       <c r="I4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1013,6 +1025,9 @@
       <c r="I5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1117,6 +1132,9 @@
       <c r="I6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1221,6 +1239,9 @@
       <c r="I7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1325,6 +1346,9 @@
       <c r="I8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1429,6 +1453,9 @@
       <c r="I9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J9" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1533,6 +1560,9 @@
       <c r="I10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1637,6 +1667,9 @@
       <c r="I11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1741,6 +1774,9 @@
       <c r="I12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1845,6 +1881,9 @@
       <c r="I13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -1949,6 +1988,9 @@
       <c r="I14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2053,6 +2095,9 @@
       <c r="I15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2157,6 +2202,9 @@
       <c r="I16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2261,6 +2309,9 @@
       <c r="I17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2365,6 +2416,9 @@
       <c r="I18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2469,6 +2523,9 @@
       <c r="I19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2573,6 +2630,9 @@
       <c r="I20" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J20" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2677,6 +2737,9 @@
       <c r="I21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2781,6 +2844,9 @@
       <c r="I22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -2885,6 +2951,9 @@
       <c r="I23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -2989,6 +3058,9 @@
       <c r="I24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3093,6 +3165,9 @@
       <c r="I25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3197,6 +3272,9 @@
       <c r="I26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3301,6 +3379,9 @@
       <c r="I27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3405,6 +3486,9 @@
       <c r="I28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3509,6 +3593,9 @@
       <c r="I29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3613,6 +3700,9 @@
       <c r="I30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3717,6 +3807,9 @@
       <c r="I31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -3821,6 +3914,9 @@
       <c r="I32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -3925,6 +4021,9 @@
       <c r="I33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4029,6 +4128,9 @@
       <c r="I34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4130,13 +4232,16 @@
       <c r="I35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="J35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 J4:AZ10 BE4:BJ10 BK4:DG33 J11:BA22 BC11:BJ22 J23:BJ33 F4:I35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 K4:AZ10 BE4:BJ10 BK4:DG33 F4:J35 K11:BA22 BC11:BJ22 K23:BJ33">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE70E011-E403-4E97-908E-59A58E185259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073E9457-28F7-4F50-AACB-F04BECB59BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atividades!$A$1:$C$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -626,7 +625,9 @@
       <c r="J1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="8"/>
+      <c r="K1" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
@@ -739,6 +740,9 @@
       <c r="J2" s="8">
         <v>46084</v>
       </c>
+      <c r="K2" s="8">
+        <v>46085</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -812,6 +816,9 @@
         <v>36</v>
       </c>
       <c r="J3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -921,6 +928,9 @@
       <c r="J4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1028,6 +1038,9 @@
       <c r="J5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1135,6 +1148,9 @@
       <c r="J6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K6" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1242,6 +1258,9 @@
       <c r="J7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1349,6 +1368,9 @@
       <c r="J8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1456,6 +1478,9 @@
       <c r="J9" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="K9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1563,6 +1588,9 @@
       <c r="J10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1670,6 +1698,9 @@
       <c r="J11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1777,6 +1808,9 @@
       <c r="J12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1884,6 +1918,9 @@
       <c r="J13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -1991,6 +2028,9 @@
       <c r="J14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2098,6 +2138,9 @@
       <c r="J15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2205,6 +2248,9 @@
       <c r="J16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2312,6 +2358,9 @@
       <c r="J17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2419,6 +2468,9 @@
       <c r="J18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2526,6 +2578,9 @@
       <c r="J19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2633,6 +2688,9 @@
       <c r="J20" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K20" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2740,6 +2798,9 @@
       <c r="J21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2847,6 +2908,9 @@
       <c r="J22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -2954,6 +3018,9 @@
       <c r="J23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3061,6 +3128,9 @@
       <c r="J24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3168,6 +3238,9 @@
       <c r="J25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3275,6 +3348,9 @@
       <c r="J26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3382,6 +3458,9 @@
       <c r="J27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3489,6 +3568,9 @@
       <c r="J28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3596,6 +3678,9 @@
       <c r="J29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3703,6 +3788,9 @@
       <c r="J30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3810,6 +3898,9 @@
       <c r="J31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -3917,6 +4008,9 @@
       <c r="J32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4024,6 +4118,9 @@
       <c r="J33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4131,6 +4228,9 @@
       <c r="J34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4235,13 +4335,16 @@
       <c r="J35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="K35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 K4:AZ10 BE4:BJ10 BK4:DG33 F4:J35 K11:BA22 BC11:BJ22 K23:BJ33">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 L4:AZ10 BE4:BJ10 BK4:DG33 L11:BA22 BC11:BJ22 L23:BJ33 F4:K35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073E9457-28F7-4F50-AACB-F04BECB59BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA163CC-D0DE-41AC-95E3-02B54DC76858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>4Faltas</t>
+  </si>
+  <si>
+    <t>Não Entregue</t>
   </si>
 </sst>
 </file>
@@ -628,7 +631,9 @@
       <c r="K1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="8"/>
+      <c r="L1" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
@@ -743,6 +748,9 @@
       <c r="K2" s="8">
         <v>46085</v>
       </c>
+      <c r="L2" s="8">
+        <v>46091</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -819,6 +827,9 @@
         <v>36</v>
       </c>
       <c r="K3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -931,6 +942,9 @@
       <c r="K4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1041,6 +1055,9 @@
       <c r="K5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1151,6 +1168,9 @@
       <c r="K6" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="L6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1261,6 +1281,9 @@
       <c r="K7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1371,6 +1394,9 @@
       <c r="K8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1481,6 +1507,9 @@
       <c r="K9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1591,6 +1620,9 @@
       <c r="K10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1701,6 +1733,9 @@
       <c r="K11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1811,6 +1846,9 @@
       <c r="K12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1921,6 +1959,9 @@
       <c r="K13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2031,6 +2072,9 @@
       <c r="K14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2141,6 +2185,9 @@
       <c r="K15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2251,6 +2298,9 @@
       <c r="K16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2361,6 +2411,9 @@
       <c r="K17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2471,6 +2524,9 @@
       <c r="K18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2581,6 +2637,9 @@
       <c r="K19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2691,6 +2750,9 @@
       <c r="K20" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L20" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2801,6 +2863,9 @@
       <c r="K21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2911,6 +2976,9 @@
       <c r="K22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3021,6 +3089,9 @@
       <c r="K23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3131,6 +3202,9 @@
       <c r="K24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L24" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3241,6 +3315,9 @@
       <c r="K25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3351,6 +3428,9 @@
       <c r="K26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3461,6 +3541,9 @@
       <c r="K27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3571,6 +3654,9 @@
       <c r="K28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3681,6 +3767,9 @@
       <c r="K29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3791,6 +3880,9 @@
       <c r="K30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3901,6 +3993,9 @@
       <c r="K31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4011,6 +4106,9 @@
       <c r="K32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4121,6 +4219,9 @@
       <c r="K33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4231,6 +4332,9 @@
       <c r="K34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L34" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4338,13 +4442,16 @@
       <c r="K35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="L35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 L4:AZ10 BE4:BJ10 BK4:DG33 L11:BA22 BC11:BJ22 L23:BJ33 F4:K35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 M4:AZ10 BE4:BJ10 BK4:DG33 M11:BA22 BC11:BJ22 M23:BJ33 F4:L35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4368,6 +4475,7 @@
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.35">
@@ -4397,8 +4505,12 @@
       <c r="D2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="E2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
@@ -4437,8 +4549,12 @@
       <c r="D3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="E3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
@@ -4475,8 +4591,12 @@
       <c r="D4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="E4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
@@ -4515,8 +4635,12 @@
       <c r="D5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="E5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -4555,8 +4679,12 @@
       <c r="D6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="E6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -4595,8 +4723,12 @@
       <c r="D7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="E7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -4635,8 +4767,12 @@
       <c r="D8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -4675,8 +4811,12 @@
       <c r="D9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -4715,8 +4855,12 @@
       <c r="D10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="E10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -4755,8 +4899,12 @@
       <c r="D11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -4795,8 +4943,12 @@
       <c r="D12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -4835,8 +4987,12 @@
       <c r="D13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="E13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -4875,8 +5031,12 @@
       <c r="D14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="E14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
@@ -4915,8 +5075,12 @@
       <c r="D15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -4953,8 +5117,12 @@
       <c r="D16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
@@ -4993,8 +5161,12 @@
       <c r="D17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="E17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -5033,8 +5205,12 @@
       <c r="D18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
@@ -5073,8 +5249,12 @@
       <c r="D19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="E19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
@@ -5113,8 +5293,12 @@
       <c r="D20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -5153,8 +5337,12 @@
       <c r="D21" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
@@ -5193,8 +5381,12 @@
       <c r="D22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -5233,8 +5425,12 @@
       <c r="D23" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="E23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -5273,8 +5469,12 @@
       <c r="D24" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="E24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -5313,8 +5513,12 @@
       <c r="D25" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="E25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
@@ -5353,8 +5557,12 @@
       <c r="D26" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="E26" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
@@ -5393,8 +5601,12 @@
       <c r="D27" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="E27" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
@@ -5433,8 +5645,12 @@
       <c r="D28" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="E28" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -5473,8 +5689,12 @@
       <c r="D29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="E29" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -5513,8 +5733,12 @@
       <c r="D30" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="E30" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -5551,8 +5775,12 @@
       <c r="D31" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="E31" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -5591,8 +5819,12 @@
       <c r="D32" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="E32" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -5629,8 +5861,12 @@
       <c r="D33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
+      <c r="E33" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
@@ -5669,8 +5905,12 @@
       <c r="D34" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+      <c r="E34" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA163CC-D0DE-41AC-95E3-02B54DC76858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF72C05-86AA-4DAB-931C-47D8607329E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -179,6 +179,15 @@
   </si>
   <si>
     <t>Não Entregue</t>
+  </si>
+  <si>
+    <t>Aula06-Lopal</t>
+  </si>
+  <si>
+    <t>Aula05-Lopal</t>
+  </si>
+  <si>
+    <t>Ramon Avila Ramalho</t>
   </si>
 </sst>
 </file>
@@ -4451,7 +4460,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 M4:AZ10 BE4:BJ10 BK4:DG33 M11:BA22 BC11:BJ22 M23:BJ33 F4:L35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 M4:AZ10 BE4:BJ10 BK4:DG33 F4:L35 M11:BA22 BC11:BJ22 M23:BJ33">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4491,6 +4500,12 @@
       <c r="D1" t="s">
         <v>43</v>
       </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
@@ -4509,7 +4524,7 @@
         <v>40</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -4815,7 +4830,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -5079,7 +5094,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -5637,7 +5652,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>40</v>
@@ -5737,7 +5752,7 @@
         <v>40</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF72C05-86AA-4DAB-931C-47D8607329E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0FF817-19F7-4AFF-B4F8-9D026EDBAFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -643,7 +643,9 @@
       <c r="L1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="8"/>
+      <c r="M1" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
@@ -760,6 +762,9 @@
       <c r="L2" s="8">
         <v>46091</v>
       </c>
+      <c r="M2" s="8">
+        <v>46092</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -839,6 +844,9 @@
         <v>36</v>
       </c>
       <c r="L3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -954,6 +962,9 @@
       <c r="L4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1067,6 +1078,9 @@
       <c r="L5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1180,6 +1194,9 @@
       <c r="L6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1293,6 +1310,9 @@
       <c r="L7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1406,6 +1426,9 @@
       <c r="L8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1519,6 +1542,9 @@
       <c r="L9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1632,6 +1658,9 @@
       <c r="L10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1745,6 +1774,9 @@
       <c r="L11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1858,6 +1890,9 @@
       <c r="L12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1971,6 +2006,9 @@
       <c r="L13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2084,6 +2122,9 @@
       <c r="L14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2197,6 +2238,9 @@
       <c r="L15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2310,6 +2354,9 @@
       <c r="L16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2423,6 +2470,9 @@
       <c r="L17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2536,6 +2586,9 @@
       <c r="L18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2649,6 +2702,9 @@
       <c r="L19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2762,6 +2818,9 @@
       <c r="L20" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="M20" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2875,6 +2934,9 @@
       <c r="L21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2988,6 +3050,9 @@
       <c r="L22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3101,6 +3166,9 @@
       <c r="L23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3214,6 +3282,9 @@
       <c r="L24" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="M24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3327,6 +3398,9 @@
       <c r="L25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3440,6 +3514,9 @@
       <c r="L26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3553,6 +3630,9 @@
       <c r="L27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3666,6 +3746,9 @@
       <c r="L28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3779,6 +3862,9 @@
       <c r="L29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3892,6 +3978,9 @@
       <c r="L30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4005,6 +4094,9 @@
       <c r="L31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4118,6 +4210,9 @@
       <c r="L32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4231,6 +4326,9 @@
       <c r="L33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4344,6 +4442,9 @@
       <c r="L34" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="M34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4454,13 +4555,16 @@
       <c r="L35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="M35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 M4:AZ10 BE4:BJ10 BK4:DG33 F4:L35 M11:BA22 BC11:BJ22 M23:BJ33">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 N4:AZ10 BE4:BJ10 BK4:DG33 F4:M35 N11:BA22 BC11:BJ22 N23:BJ33">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0FF817-19F7-4AFF-B4F8-9D026EDBAFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915ABEE-DB78-4DA7-9041-33A68780E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -646,8 +646,12 @@
       <c r="M1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
+      <c r="N1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
       <c r="R1" s="8"/>
@@ -765,6 +769,12 @@
       <c r="M2" s="8">
         <v>46092</v>
       </c>
+      <c r="N2" s="8">
+        <v>46098</v>
+      </c>
+      <c r="O2" s="8">
+        <v>46099</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -847,6 +857,9 @@
         <v>36</v>
       </c>
       <c r="M3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -965,6 +978,9 @@
       <c r="M4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1081,6 +1097,9 @@
       <c r="M5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1197,6 +1216,9 @@
       <c r="M6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1313,6 +1335,9 @@
       <c r="M7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1429,6 +1454,9 @@
       <c r="M8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1545,6 +1573,9 @@
       <c r="M9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1661,6 +1692,9 @@
       <c r="M10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1777,6 +1811,9 @@
       <c r="M11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1893,6 +1930,9 @@
       <c r="M12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2009,6 +2049,9 @@
       <c r="M13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2125,6 +2168,9 @@
       <c r="M14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2241,6 +2287,9 @@
       <c r="M15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2357,6 +2406,9 @@
       <c r="M16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2473,6 +2525,9 @@
       <c r="M17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O17" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2589,6 +2644,9 @@
       <c r="M18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2705,6 +2763,9 @@
       <c r="M19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2821,6 +2882,9 @@
       <c r="M20" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="O20" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2937,6 +3001,9 @@
       <c r="M21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3053,6 +3120,9 @@
       <c r="M22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3169,6 +3239,9 @@
       <c r="M23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3285,6 +3358,9 @@
       <c r="M24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3401,6 +3477,9 @@
       <c r="M25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3517,6 +3596,9 @@
       <c r="M26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3633,6 +3715,9 @@
       <c r="M27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3749,6 +3834,9 @@
       <c r="M28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O28" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3865,6 +3953,9 @@
       <c r="M29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3981,6 +4072,9 @@
       <c r="M30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4097,6 +4191,9 @@
       <c r="M31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4213,6 +4310,9 @@
       <c r="M32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4329,6 +4429,9 @@
       <c r="M33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4445,6 +4548,9 @@
       <c r="M34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4558,13 +4664,16 @@
       <c r="M35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="O35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 N4:AZ10 BE4:BJ10 BK4:DG33 F4:M35 N11:BA22 BC11:BJ22 N23:BJ33">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 BE4:BJ10 BK4:DG33 F4:M35 BC11:BJ22 N4:N33 P23:BJ33 P11:BA22 P4:AZ10 O4:O35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915ABEE-DB78-4DA7-9041-33A68780E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EBBA35-1624-47BE-9751-ED3BAF7620EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -652,7 +652,9 @@
       <c r="O1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="8"/>
+      <c r="P1" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="Q1" s="8"/>
       <c r="R1" s="8"/>
       <c r="S1" s="1"/>
@@ -775,6 +777,9 @@
       <c r="O2" s="8">
         <v>46099</v>
       </c>
+      <c r="P2" s="8">
+        <v>46120</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -860,6 +865,9 @@
         <v>36</v>
       </c>
       <c r="O3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -981,6 +989,9 @@
       <c r="O4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1100,6 +1111,9 @@
       <c r="O5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1219,6 +1233,9 @@
       <c r="O6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1338,6 +1355,9 @@
       <c r="O7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1457,6 +1477,9 @@
       <c r="O8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1576,6 +1599,9 @@
       <c r="O9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1695,6 +1721,9 @@
       <c r="O10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1814,6 +1843,9 @@
       <c r="O11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1933,6 +1965,9 @@
       <c r="O12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2052,6 +2087,9 @@
       <c r="O13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2171,6 +2209,9 @@
       <c r="O14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2290,6 +2331,9 @@
       <c r="O15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2409,6 +2453,9 @@
       <c r="O16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2528,6 +2575,9 @@
       <c r="O17" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="P17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2647,6 +2697,9 @@
       <c r="O18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2766,6 +2819,9 @@
       <c r="O19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2885,6 +2941,9 @@
       <c r="O20" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="P20" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3004,6 +3063,9 @@
       <c r="O21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3123,6 +3185,9 @@
       <c r="O22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3242,6 +3307,9 @@
       <c r="O23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3361,6 +3429,9 @@
       <c r="O24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3480,6 +3551,9 @@
       <c r="O25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3599,6 +3673,9 @@
       <c r="O26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3718,6 +3795,9 @@
       <c r="O27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3837,6 +3917,9 @@
       <c r="O28" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P28" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3956,6 +4039,9 @@
       <c r="O29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4075,6 +4161,9 @@
       <c r="O30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4194,6 +4283,9 @@
       <c r="O31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4313,6 +4405,9 @@
       <c r="O32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4432,6 +4527,9 @@
       <c r="O33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4551,6 +4649,9 @@
       <c r="O34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4667,13 +4768,16 @@
       <c r="O35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="P35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 BE4:BJ10 BK4:DG33 F4:M35 BC11:BJ22 N4:N33 P23:BJ33 P11:BA22 P4:AZ10 O4:O35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 Q4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 Q11:BA22 BC11:BJ22 Q23:BJ33 O4:P35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EBBA35-1624-47BE-9751-ED3BAF7620EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8272A2-A4CB-4537-A6DD-10AFEDFB5270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -655,7 +655,9 @@
       <c r="P1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="8"/>
+      <c r="Q1" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="R1" s="8"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
@@ -780,6 +782,9 @@
       <c r="P2" s="8">
         <v>46120</v>
       </c>
+      <c r="Q2" s="8">
+        <v>46126</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -868,6 +873,9 @@
         <v>36</v>
       </c>
       <c r="P3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="9" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -992,6 +1000,9 @@
       <c r="P4" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q4" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1114,6 +1125,9 @@
       <c r="P5" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q5" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1236,6 +1250,9 @@
       <c r="P6" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q6" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1358,6 +1375,9 @@
       <c r="P7" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q7" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1480,6 +1500,9 @@
       <c r="P8" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q8" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1602,6 +1625,9 @@
       <c r="P9" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1724,6 +1750,9 @@
       <c r="P10" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q10" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1846,6 +1875,9 @@
       <c r="P11" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q11" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1968,6 +2000,9 @@
       <c r="P12" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q12" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -2090,6 +2125,9 @@
       <c r="P13" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2212,6 +2250,9 @@
       <c r="P14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2334,6 +2375,9 @@
       <c r="P15" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q15" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2456,6 +2500,9 @@
       <c r="P16" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q16" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2578,6 +2625,9 @@
       <c r="P17" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2700,6 +2750,9 @@
       <c r="P18" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q18" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2822,6 +2875,9 @@
       <c r="P19" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q19" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2944,6 +3000,9 @@
       <c r="P20" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="Q20" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -3066,6 +3125,9 @@
       <c r="P21" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q21" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3188,6 +3250,9 @@
       <c r="P22" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q22" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3310,6 +3375,9 @@
       <c r="P23" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q23" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3432,6 +3500,9 @@
       <c r="P24" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q24" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3554,6 +3625,9 @@
       <c r="P25" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q25" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3676,6 +3750,9 @@
       <c r="P26" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q26" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3798,6 +3875,9 @@
       <c r="P27" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q27" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3920,6 +4000,9 @@
       <c r="P28" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="Q28" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -4042,6 +4125,9 @@
       <c r="P29" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4164,6 +4250,9 @@
       <c r="P30" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q30" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4286,6 +4375,9 @@
       <c r="P31" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q31" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4408,6 +4500,9 @@
       <c r="P32" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q32" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4530,6 +4625,9 @@
       <c r="P33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -4652,6 +4750,9 @@
       <c r="P34" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q34" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
       <c r="BB34" s="5"/>
@@ -4771,13 +4872,16 @@
       <c r="P35" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="Q35" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 Q4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 Q11:BA22 BC11:BJ22 Q23:BJ33 O4:P35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 R4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 R11:BA22 BC11:BJ22 R23:BJ33 O4:Q35">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8272A2-A4CB-4537-A6DD-10AFEDFB5270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCEB10E-F1D8-4712-9731-9988E6276C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -4001,7 +4001,7 @@
         <v>37</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
@@ -4619,6 +4619,9 @@
       <c r="M33" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="N33" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="O33" s="9" t="s">
         <v>36</v>
       </c>
@@ -4751,7 +4754,7 @@
         <v>36</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AZ34" s="5"/>
       <c r="BA34" s="5"/>
@@ -4881,7 +4884,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 R4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 R11:BA22 BC11:BJ22 R23:BJ33 O4:Q35">
+  <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 R4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 O4:Q35 R11:BA22 BC11:BJ22 R23:BJ33">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5165,7 +5168,9 @@
       <c r="F7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCEB10E-F1D8-4712-9731-9988E6276C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30745A8-3934-4597-95E2-901F2F57007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="50">
   <si>
     <t>Aluno</t>
   </si>
@@ -4909,6 +4909,7 @@
     <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.35">
@@ -5036,7 +5037,9 @@
       <c r="F4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
@@ -5080,7 +5083,9 @@
       <c r="F5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
@@ -5124,7 +5129,9 @@
       <c r="F6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -5169,7 +5176,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -5258,7 +5265,9 @@
       <c r="F9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
@@ -5346,7 +5355,9 @@
       <c r="F11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
@@ -5390,7 +5401,9 @@
       <c r="F12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
@@ -5434,7 +5447,9 @@
       <c r="F13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
@@ -5478,7 +5493,9 @@
       <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="11"/>
+      <c r="G14" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
@@ -5522,7 +5539,9 @@
       <c r="F15" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
@@ -5564,7 +5583,9 @@
       <c r="F16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="11"/>
+      <c r="G16" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
@@ -5608,7 +5629,9 @@
       <c r="F17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
@@ -5652,7 +5675,9 @@
       <c r="F18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="11"/>
+      <c r="G18" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
@@ -5696,7 +5721,9 @@
       <c r="F19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="11"/>
+      <c r="G19" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
@@ -5740,7 +5767,9 @@
       <c r="F20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
@@ -5784,7 +5813,9 @@
       <c r="F21" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
@@ -5828,7 +5859,9 @@
       <c r="F22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="11"/>
+      <c r="G22" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
@@ -5872,7 +5905,9 @@
       <c r="F23" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="11"/>
+      <c r="G23" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
@@ -5916,7 +5951,9 @@
       <c r="F24" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G24" s="11"/>
+      <c r="G24" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
@@ -6004,7 +6041,9 @@
       <c r="F26" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G26" s="11"/>
+      <c r="G26" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
@@ -6048,7 +6087,9 @@
       <c r="F27" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="11"/>
+      <c r="G27" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
@@ -6092,7 +6133,9 @@
       <c r="F28" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G28" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
@@ -6136,7 +6179,9 @@
       <c r="F29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="11"/>
+      <c r="G29" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
@@ -6180,7 +6225,9 @@
       <c r="F30" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
@@ -6222,7 +6269,9 @@
       <c r="F31" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="11"/>
+      <c r="G31" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
@@ -6266,7 +6315,9 @@
       <c r="F32" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G32" s="11"/>
+      <c r="G32" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
@@ -6308,7 +6359,9 @@
       <c r="F33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G33" s="11"/>
+      <c r="G33" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
@@ -6352,7 +6405,9 @@
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G34" s="11"/>
+      <c r="G34" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30745A8-3934-4597-95E2-901F2F57007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F790949-1273-485C-B38C-1B8D574C2406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
     <sheet name="Atividades" sheetId="2" r:id="rId2"/>
+    <sheet name="LOPAL1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atividades!$A$1:$C$34</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="53">
   <si>
     <t>Aluno</t>
   </si>
@@ -188,6 +189,15 @@
   </si>
   <si>
     <t>Ramon Avila Ramalho</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Média</t>
   </si>
 </sst>
 </file>
@@ -6451,4 +6461,286 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD89518-5B40-4FB4-8DB1-CAF2F40E7C9B}">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2">
+        <f>AVERAGE(B2:B30,B33)</f>
+        <v>65.333333333333329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B33">
+    <sortCondition ref="A2:A33"/>
+  </sortState>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F790949-1273-485C-B38C-1B8D574C2406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACE9A6A-5963-4BCE-9B7F-C7F0B4B78C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -306,7 +306,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -4895,12 +4905,12 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 R4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 O4:Q35 R11:BA22 BC11:BJ22 R23:BJ33">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6449,7 +6459,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="C2:AD34">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Entregue"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6741,6 +6751,11 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B33">
     <sortCondition ref="A2:A33"/>
   </sortState>
+  <conditionalFormatting sqref="B2:B33">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACE9A6A-5963-4BCE-9B7F-C7F0B4B78C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9102312D-50D4-40FC-9D7A-38F70856F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="54">
   <si>
     <t>Aluno</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Média</t>
+  </si>
+  <si>
+    <t>N2</t>
   </si>
 </sst>
 </file>
@@ -6489,6 +6492,9 @@
       <c r="B1" t="s">
         <v>50</v>
       </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -6497,6 +6503,9 @@
       <c r="B2">
         <v>40</v>
       </c>
+      <c r="C2">
+        <v>85</v>
+      </c>
       <c r="E2" t="s">
         <v>52</v>
       </c>
@@ -6512,6 +6521,9 @@
       <c r="B3">
         <v>15</v>
       </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -6528,6 +6540,9 @@
       <c r="B5">
         <v>50</v>
       </c>
+      <c r="C5">
+        <v>85</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -6536,6 +6551,9 @@
       <c r="B6">
         <v>60</v>
       </c>
+      <c r="C6">
+        <v>70</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -6544,6 +6562,9 @@
       <c r="B7">
         <v>50</v>
       </c>
+      <c r="C7">
+        <v>70</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -6560,6 +6581,9 @@
       <c r="B9">
         <v>40</v>
       </c>
+      <c r="C9">
+        <v>70</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -6576,6 +6600,9 @@
       <c r="B11">
         <v>65</v>
       </c>
+      <c r="C11">
+        <v>75</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -6600,6 +6627,9 @@
       <c r="B14">
         <v>70</v>
       </c>
+      <c r="C14">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -6608,6 +6638,9 @@
       <c r="B15">
         <v>80</v>
       </c>
+      <c r="C15">
+        <v>85</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -6617,15 +6650,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -6633,31 +6669,40 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="B19">
         <v>80</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C19">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
       <c r="B20">
         <v>85</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
       <c r="B21">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -6665,39 +6710,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23">
         <v>60</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C23">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
       <c r="B24">
         <v>50</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C24">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>10</v>
       </c>
       <c r="B25">
         <v>85</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>12</v>
       </c>
       <c r="B26">
         <v>65</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C26">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -6705,7 +6762,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -6713,7 +6770,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -6721,7 +6778,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -6729,14 +6786,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C31">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>28</v>
+      </c>
+      <c r="C32">
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">

--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9102312D-50D4-40FC-9D7A-38F70856F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059E9185-4F73-410F-A676-D626AF0825BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
     <sheet name="Atividades" sheetId="2" r:id="rId2"/>
     <sheet name="LOPAL1" sheetId="3" r:id="rId3"/>
+    <sheet name="LER" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Atividades!$A$1:$C$34</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="59">
   <si>
     <t>Aluno</t>
   </si>
@@ -194,20 +195,35 @@
     <t>N1</t>
   </si>
   <si>
-    <t>Nome</t>
-  </si>
-  <si>
     <t>Média</t>
   </si>
   <si>
     <t>N2</t>
+  </si>
+  <si>
+    <t>Alunos</t>
+  </si>
+  <si>
+    <t>Grupo 1:</t>
+  </si>
+  <si>
+    <t>Grupo 1 Nota:</t>
+  </si>
+  <si>
+    <t>Grupo 2 Nota:</t>
+  </si>
+  <si>
+    <t>Grupo 3 Nota:</t>
+  </si>
+  <si>
+    <t>Grupo 2:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +251,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -284,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -302,6 +326,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6486,14 +6513,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
-        <v>53</v>
+      <c r="C1" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -6507,7 +6534,7 @@
         <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <f>AVERAGE(B2:B30,B33)</f>
@@ -6821,4 +6848,302 @@
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E55F04-3513-4B74-BAD6-A6A9AFAB1BA2}">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3">
+        <f>B36</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9">
+        <f>B36</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12">
+        <f>B36</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23">
+        <f>B38</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24">
+        <f>B36</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31">
+        <f>B36</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33">
+        <f>B36</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/ds/seduc/1des/frequencia.xlsx
+++ b/ds/seduc/1des/frequencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\ds\seduc\1des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059E9185-4F73-410F-A676-D626AF0825BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694EE514-9F7A-45D8-9D1D-D17E8FC2F2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="595" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="65">
   <si>
     <t>Aluno</t>
   </si>
@@ -218,6 +218,24 @@
   <si>
     <t>Grupo 2:</t>
   </si>
+  <si>
+    <t>Grupo 3:</t>
+  </si>
+  <si>
+    <t>Grupo 4 Nota:</t>
+  </si>
+  <si>
+    <t>Grupo 4:</t>
+  </si>
+  <si>
+    <t>Média 2</t>
+  </si>
+  <si>
+    <t>Grupo 5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo 5 Nota: </t>
+  </si>
 </sst>
 </file>
 
@@ -336,7 +354,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4935,12 +4973,12 @@
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="F3:AZ3 BE3:DG3 BB3:BB22 D3:E35 R4:AZ10 BE4:BJ10 N4:N33 BK4:DG33 F4:M35 O4:Q35 R11:BA22 BC11:BJ22 R23:BJ33">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6489,7 +6527,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="C2:AD34">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Entregue"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6505,14 +6543,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD89518-5B40-4FB4-8DB1-CAF2F40E7C9B}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>53</v>
       </c>
@@ -6522,8 +6560,11 @@
       <c r="C1" s="13" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D1" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6533,34 +6574,53 @@
       <c r="C2">
         <v>85</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2">
+        <f>AVERAGE(B2:C2)</f>
+        <v>62.5</v>
+      </c>
+      <c r="F2" t="s">
         <v>51</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <f>AVERAGE(B2:B30,B33)</f>
-        <v>65.333333333333329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D33" si="0">AVERAGE(B3:C3)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4">
+        <f>AVERAGE(C2:C33)</f>
+        <v>78.421052631578945</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6630,12 @@
       <c r="C5">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -6581,8 +6645,12 @@
       <c r="C6">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -6592,16 +6660,24 @@
       <c r="C7">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -6611,16 +6687,24 @@
       <c r="C9">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
       <c r="B10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -6630,24 +6714,36 @@
       <c r="C11">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13">
         <v>95</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -6657,8 +6753,12 @@
       <c r="C14">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -6668,16 +6768,24 @@
       <c r="C15">
         <v>85</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -6687,16 +6795,24 @@
       <c r="C17">
         <v>65</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
       <c r="B18">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -6706,8 +6822,12 @@
       <c r="C19">
         <v>95</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -6717,8 +6837,12 @@
       <c r="C20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -6728,16 +6852,24 @@
       <c r="C21">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>11</v>
       </c>
       <c r="B22">
         <v>65</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6747,8 +6879,12 @@
       <c r="C23">
         <v>70</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -6758,8 +6894,12 @@
       <c r="C24">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -6769,8 +6909,12 @@
       <c r="C25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -6780,60 +6924,92 @@
       <c r="C26">
         <v>75</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28">
         <v>85</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>19</v>
       </c>
       <c r="B29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
       <c r="C31">
         <v>75</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="C32">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>21</v>
       </c>
       <c r="B33">
+        <v>70</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
     </row>
@@ -6842,6 +7018,11 @@
     <sortCondition ref="A2:A33"/>
   </sortState>
   <conditionalFormatting sqref="B2:B33">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>50</formula>
     </cfRule>
@@ -6852,7 +7033,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E55F04-3513-4B74-BAD6-A6A9AFAB1BA2}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.81640625" bestFit="1" customWidth="1"/>
@@ -6892,21 +7073,49 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4">
+        <f>B40</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5">
+        <f>B42</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6">
+        <f>B40</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <f>B42</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -6948,6 +7157,13 @@
       <c r="A11" t="s">
         <v>23</v>
       </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11">
+        <f>B44</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -6989,6 +7205,13 @@
       <c r="A15" t="s">
         <v>31</v>
       </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15">
+        <f>B42</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -7006,6 +7229,13 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17">
+        <f>B40</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
@@ -7016,16 +7246,37 @@
       <c r="A19" t="s">
         <v>9</v>
       </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19">
+        <f>B44</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>6</v>
       </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <f>B44</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>44</v>
       </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21">
+        <f>B42</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
@@ -7067,11 +7318,25 @@
       <c r="A25" t="s">
         <v>10</v>
       </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25">
+        <f>B44</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>12</v>
       </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26">
+        <f>B40</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
@@ -7082,16 +7347,37 @@
       <c r="A28" t="s">
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28">
+        <f>B40</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>19</v>
       </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29">
+        <f>B42</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30">
+        <f>B42</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
@@ -7109,6 +7395,13 @@
       <c r="A32" t="s">
         <v>28</v>
       </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32">
+        <f>B44</f>
+        <v>85</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
@@ -7141,6 +7434,25 @@
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>57</v>
+      </c>
+      <c r="B40">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
